--- a/reports/devops-jobs-israel-2026-W29.xlsx
+++ b/reports/devops-jobs-israel-2026-W29.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="467">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-13T09:43:55</t>
+    <t xml:space="preserve">2026-07-14T08:23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0%</t>
+    <t xml:space="preserve">2.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -417,1017 +417,957 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4437214837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid–Senior DevOps Engineer (Kubernetes / Edge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid%E2%80%93senior-devops-engineer-kubernetes-edge-at-cybord-4440020866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4440389172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4440042602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4437657015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Jerusalem</t>
   </si>
   <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4437214837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyndryl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kyndryl-4439135082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437309963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobscroller-4438924143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kadima, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437759387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataspan.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer (36900)</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36900-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439717780</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4439771613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4438646614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437766169</t>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobscroller-4438942609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harel Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4439703721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (36856)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-36856-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439722636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4438598493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4436692890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4437215091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLSTARSIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-system-administrator-at-allstarsit-4440065050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Dropit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4438594459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AM Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4434847048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobscroller-4438924143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer (Agentic Workflows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corephotonics Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-agentic-workflows-at-corephotonics-ltd-4437212081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataspan.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4438598493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4439138209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4439703721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4439750230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (36856)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-36856-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439722636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4436692890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4437215091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36759)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, GCP, Cloud (any), Kubernetes, CI/CD, Terraform/IaC, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438227753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MER Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4429038091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1437,19 +1377,22 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1601,7 +1544,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -1609,7 +1552,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1617,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1625,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>954</v>
+        <v>968</v>
       </c>
     </row>
     <row r="10">
@@ -1697,7 +1640,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1705,7 +1648,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1724,36 +1667,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1761,7 +1704,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1780,130 +1723,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>470</v>
+        <v>343</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>311</v>
+        <v>452</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>474</v>
+        <v>315</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>475</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>476</v>
+        <v>353</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>456</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>457</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1928,13 +1871,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
@@ -1942,13 +1885,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1957,88 +1900,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3">
-        <v>37.7</v>
+        <v>36.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>38.7</v>
+        <v>31.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.6</v>
+        <v>19.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.8</v>
+        <v>14.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2122,7 +2065,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -2154,7 +2097,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2186,7 +2129,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -2218,7 +2161,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -2250,7 +2193,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -2282,7 +2225,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -2314,7 +2257,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -2346,7 +2289,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -2378,7 +2321,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -2410,7 +2353,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -2442,7 +2385,7 @@
         <v>72</v>
       </c>
       <c r="J12" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -2474,7 +2417,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2449,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2538,7 +2481,7 @@
         <v>96</v>
       </c>
       <c r="J15" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -2570,7 +2513,7 @@
         <v>79</v>
       </c>
       <c r="J16" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -2602,7 +2545,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -2634,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -2666,7 +2609,7 @@
         <v>111</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2698,7 +2641,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
@@ -2730,7 +2673,7 @@
         <v>121</v>
       </c>
       <c r="J21" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -2762,7 +2705,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
@@ -2794,7 +2737,7 @@
         <v>131</v>
       </c>
       <c r="J23" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -2811,20 +2754,22 @@
         <v>44</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -2832,10 +2777,10 @@
         <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>44</v>
@@ -2844,24 +2789,24 @@
         <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="J25" s="3">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>139</v>
@@ -2870,14 +2815,14 @@
         <v>140</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>141</v>
@@ -2886,56 +2831,54 @@
         <v>142</v>
       </c>
       <c r="J26" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J27" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
@@ -2948,7 +2891,7 @@
         <v>150</v>
       </c>
       <c r="J28" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2962,7 +2905,7 @@
         <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2972,10 +2915,10 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2983,32 +2926,32 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="D30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3016,13 +2959,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -3032,57 +2975,59 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="J32" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3092,10 +3037,10 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3103,16 +3048,16 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>45</v>
@@ -3122,114 +3067,114 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J35" s="3">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>44</v>
@@ -3237,91 +3182,89 @@
       <c r="E38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>186</v>
-      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="J38" s="3">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>44</v>
@@ -3334,43 +3277,43 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -3378,13 +3321,13 @@
         <v>112</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>45</v>
@@ -3394,24 +3337,24 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
@@ -3424,40 +3367,40 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -3465,62 +3408,62 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J46" s="3">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>44</v>
+        <v>214</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -3528,10 +3471,10 @@
         <v>112</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
@@ -3544,27 +3487,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="J48" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3574,174 +3517,176 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="J50" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>223</v>
       </c>
       <c r="J51" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>226</v>
+        <v>159</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>49</v>
+        <v>235</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J54" s="3">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>49</v>
+        <v>243</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
@@ -3754,24 +3699,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>163</v>
+        <v>86</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
@@ -3784,84 +3729,84 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="J58" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>44</v>
@@ -3874,114 +3819,114 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="J59" s="3">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="J62" s="3">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>112</v>
+        <v>264</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>44</v>
@@ -3994,87 +3939,87 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="J63" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>49</v>
+        <v>267</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="J64" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>264</v>
+        <v>52</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>261</v>
+        <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>45</v>
@@ -4084,24 +4029,24 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>49</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
@@ -4114,13 +4059,13 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
@@ -4128,10 +4073,10 @@
         <v>49</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>44</v>
@@ -4144,84 +4089,84 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="J68" s="3">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>52</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>86</v>
+        <v>223</v>
       </c>
       <c r="J69" s="3">
-        <v>59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>275</v>
+        <v>52</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>277</v>
+        <v>159</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>280</v>
+        <v>143</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>118</v>
@@ -4234,24 +4179,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="J71" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>44</v>
@@ -4264,10 +4209,10 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>228</v>
+        <v>142</v>
       </c>
       <c r="J72" s="3">
         <v>1</v>
@@ -4275,73 +4220,73 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>226</v>
+        <v>147</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>44</v>
@@ -4354,27 +4299,27 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>112</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>296</v>
+        <v>156</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>45</v>
@@ -4384,87 +4329,91 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>283</v>
+        <v>154</v>
       </c>
       <c r="J76" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>296</v>
+        <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>283</v>
+        <v>142</v>
       </c>
       <c r="J77" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
       <c r="J78" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>38</v>
@@ -4474,27 +4423,27 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>38</v>
@@ -4504,86 +4453,86 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="J80" s="3">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>161</v>
+        <v>289</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>310</v>
+        <v>56</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>311</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="J81" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>112</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>212</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>44</v>
+        <v>214</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F82" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>315</v>
+        <v>142</v>
       </c>
       <c r="J82" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>112</v>
+        <v>317</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>44</v>
@@ -4596,91 +4545,87 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>318</v>
+        <v>154</v>
       </c>
       <c r="J83" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>42</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>186</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="J84" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>56</v>
+        <v>325</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>324</v>
-      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>189</v>
+        <v>328</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>45</v>
@@ -4690,27 +4635,27 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>45</v>
@@ -4720,10 +4665,10 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J87" s="3">
         <v>0</v>
@@ -4731,31 +4676,29 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>186</v>
-      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4763,13 +4706,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>44</v>
@@ -4777,29 +4720,31 @@
       <c r="E89" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="J89" s="3">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>112</v>
+        <v>339</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>118</v>
@@ -4812,321 +4757,109 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>169</v>
+        <v>346</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>186</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>281</v>
+        <v>56</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J94" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J95" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J96" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J97" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J98" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J99" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J100" s="3">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
+  <autoFilter ref="A1:J93"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5220,13 +4953,6 @@
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5234,8 +4960,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5271,10 +4997,10 @@
         <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5282,7 +5008,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
@@ -5290,10 +5016,10 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5301,18 +5027,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5320,18 +5046,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5339,18 +5065,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5358,18 +5084,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5377,18 +5103,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5396,18 +5122,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5415,18 +5141,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>255</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5434,18 +5160,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5453,18 +5179,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5472,18 +5198,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5491,18 +5217,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>189</v>
+        <v>332</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5510,18 +5236,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5529,87 +5255,11 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5625,10 +5275,6 @@
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5642,15 +5288,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -5658,7 +5304,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5666,7 +5312,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>369</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5674,15 +5320,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5690,7 +5336,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5698,23 +5344,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5722,7 +5368,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5730,15 +5376,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5746,7 +5392,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5754,7 +5400,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5762,7 +5408,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5784,7 +5430,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5805,7 +5451,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5813,7 +5459,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5821,15 +5467,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5837,7 +5483,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5845,7 +5491,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5853,7 +5499,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5861,7 +5507,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5869,7 +5515,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5877,7 +5523,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5885,7 +5531,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5893,7 +5539,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>295</v>
+        <v>221</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5901,10 +5547,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5922,16 +5568,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5967,13 +5613,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>6.7</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -5981,10 +5627,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -5995,10 +5641,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="C6" s="3">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -6009,13 +5655,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6023,13 +5669,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="C8" s="3">
         <v>4.6</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6037,10 +5683,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -6065,13 +5711,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6079,10 +5725,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -6093,10 +5739,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -6107,10 +5753,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6121,13 +5767,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6135,10 +5781,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6161,15 +5807,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -6183,10 +5829,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
@@ -6194,10 +5840,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -6216,7 +5862,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -6224,7 +5870,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -6237,31 +5883,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6269,7 +5915,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6277,10 +5923,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6292,7 +5938,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6304,10 +5950,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6319,10 +5965,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6339,31 +5985,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -6371,31 +6017,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
@@ -6403,31 +6049,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>318</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -6435,31 +6081,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>402</v>
+        <v>317</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>403</v>
+        <v>143</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>56</v>
+        <v>286</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6">
@@ -6467,31 +6113,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>407</v>
+        <v>139</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>165</v>
+        <v>329</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>121</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7">
@@ -6499,31 +6145,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
+        <v>392</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
@@ -6531,31 +6177,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>169</v>
+        <v>397</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F8" s="3">
+        <v>68</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F8" s="3">
-        <v>76</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>228</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -6563,31 +6209,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>161</v>
+        <v>401</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="F9" s="3">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>421</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -6595,31 +6241,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>170</v>
+        <v>405</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F10" s="3">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>163</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11">
@@ -6627,31 +6273,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>424</v>
+        <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>425</v>
+        <v>128</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F11" s="3">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -6659,31 +6305,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>429</v>
+        <v>159</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F12" s="3">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>228</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13">
@@ -6691,31 +6337,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>432</v>
+        <v>59</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>433</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>434</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>318</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -6723,31 +6369,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F14" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -6755,31 +6401,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F15" s="3">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>446</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16">
@@ -6787,31 +6433,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F16" s="3">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17">
@@ -6819,31 +6465,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>452</v>
+        <v>397</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>435</v>
+        <v>382</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>455</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18">
@@ -6851,31 +6497,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>450</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
@@ -6883,31 +6529,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>127</v>
+        <v>436</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>86</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20">
@@ -6915,31 +6561,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>317</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>440</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>61</v>
+        <v>442</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21">
@@ -6947,31 +6593,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W29.xlsx
+++ b/reports/devops-jobs-israel-2026-W29.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-14T08:23:20</t>
+    <t xml:space="preserve">2026-07-15T08:29:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2%</t>
+    <t xml:space="preserve">2.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -438,6 +438,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-infinidat-4437658931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA AI</t>
   </si>
   <si>
@@ -450,12 +465,33 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
+    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
   </si>
   <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
   </si>
   <si>
@@ -474,6 +510,27 @@
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">HISKY</t>
   </si>
   <si>
@@ -483,889 +540,895 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid–Senior DevOps Engineer (Kubernetes / Edge)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybord</t>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4440042602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harel Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeerSpot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4438051951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobscroller-4438942609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36900-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439717780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4438598493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Facing System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4435649753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4437678341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belocal Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4439138209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (36856)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-36856-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439722636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4436692890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4437215091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid%E2%80%93senior-devops-engineer-kubernetes-edge-at-cybord-4440020866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4440389172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4440042602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AM Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4437657015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobscroller-4438924143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
   </si>
   <si>
     <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kadima, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437759387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataspan.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36900-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439717780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobscroller-4438942609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harel Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4439703721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (36856)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-36856-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439722636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4438598493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4436692890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4437215091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLSTARSIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-system-administrator-at-allstarsit-4440065050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remedio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
   </si>
   <si>
     <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1377,12 +1440,12 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
@@ -1390,9 +1453,6 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1544,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1552,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1560,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1568,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>968</v>
+        <v>981</v>
       </c>
     </row>
     <row r="10">
@@ -1640,7 +1700,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1667,36 +1727,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1704,7 +1764,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1723,63 +1783,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>343</v>
+        <v>471</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>454</v>
+        <v>326</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>474</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
@@ -1787,7 +1847,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>359</v>
+        <v>475</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
@@ -1795,7 +1855,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>476</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -1803,31 +1863,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>456</v>
+        <v>368</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1835,18 +1895,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>457</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1871,13 +1931,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
@@ -1888,10 +1948,10 @@
         <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>14.1</v>
+        <v>13.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1900,88 +1960,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>36.3</v>
+        <v>32.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.7</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.6</v>
+        <v>37.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.6</v>
+        <v>20.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.7</v>
+        <v>16.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1993,8 +2053,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2065,7 +2125,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -2097,7 +2157,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -2129,7 +2189,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -2161,7 +2221,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -2193,7 +2253,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -2225,7 +2285,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -2257,7 +2317,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -2289,7 +2349,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -2321,7 +2381,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -2353,7 +2413,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -2385,7 +2445,7 @@
         <v>72</v>
       </c>
       <c r="J12" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -2417,7 +2477,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2449,7 +2509,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2481,7 +2541,7 @@
         <v>96</v>
       </c>
       <c r="J15" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2513,7 +2573,7 @@
         <v>79</v>
       </c>
       <c r="J16" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -2545,7 +2605,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -2577,7 +2637,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -2609,7 +2669,7 @@
         <v>111</v>
       </c>
       <c r="J19" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2641,7 +2701,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -2673,7 +2733,7 @@
         <v>121</v>
       </c>
       <c r="J21" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -2705,7 +2765,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
@@ -2737,7 +2797,7 @@
         <v>131</v>
       </c>
       <c r="J23" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -2769,7 +2829,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -2801,37 +2861,39 @@
         <v>79</v>
       </c>
       <c r="J25" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2839,10 +2901,10 @@
         <v>112</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
@@ -2855,43 +2917,43 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="J27" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J28" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2902,10 +2964,10 @@
         <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2915,27 +2977,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -2945,18 +3007,18 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>158</v>
@@ -2968,41 +3030,39 @@
         <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
@@ -3010,24 +3070,24 @@
         <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3037,13 +3097,13 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3051,10 +3111,10 @@
         <v>112</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>118</v>
@@ -3067,43 +3127,43 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="J34" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="J35" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3111,10 +3171,10 @@
         <v>112</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>118</v>
@@ -3127,27 +3187,27 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
@@ -3157,13 +3217,13 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -3171,13 +3231,13 @@
         <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>45</v>
@@ -3187,57 +3247,57 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="J38" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -3247,24 +3307,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>44</v>
@@ -3272,26 +3332,28 @@
       <c r="E41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J41" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>159</v>
@@ -3300,37 +3362,37 @@
         <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3340,10 +3402,10 @@
         <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -3351,26 +3413,26 @@
         <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="J44" s="3">
         <v>1</v>
@@ -3378,10 +3440,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>159</v>
@@ -3390,7 +3452,7 @@
         <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3400,127 +3462,129 @@
         <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="J47" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J48" s="3">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>223</v>
+        <v>147</v>
       </c>
       <c r="J49" s="3">
         <v>2</v>
@@ -3528,16 +3592,16 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>226</v>
+        <v>149</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3547,54 +3611,56 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>230</v>
+        <v>56</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F51" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>223</v>
+        <v>79</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>44</v>
@@ -3607,27 +3673,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>237</v>
+        <v>159</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>45</v>
@@ -3637,59 +3703,57 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>240</v>
-      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>242</v>
+        <v>143</v>
       </c>
       <c r="J54" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>44</v>
+        <v>235</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3699,114 +3763,114 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="J55" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="J57" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>44</v>
@@ -3819,27 +3883,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>45</v>
@@ -3849,27 +3913,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3879,10 +3943,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3890,76 +3954,76 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="J62" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>264</v>
+        <v>49</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>159</v>
+        <v>257</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>44</v>
+        <v>258</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>45</v>
@@ -3969,84 +4033,84 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J64" s="3">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>49</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
@@ -4059,21 +4123,21 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="J67" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>159</v>
@@ -4082,34 +4146,34 @@
         <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="J68" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>45</v>
@@ -4119,13 +4183,13 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="J69" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4133,10 +4197,10 @@
         <v>52</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>44</v>
@@ -4149,70 +4213,70 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J70" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>143</v>
+        <v>282</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="J71" s="3">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="J72" s="3">
         <v>1</v>
@@ -4220,16 +4284,16 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>38</v>
@@ -4239,167 +4303,163 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="J74" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>147</v>
+        <v>293</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="J75" s="3">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>154</v>
+        <v>278</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>206</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>240</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="I78" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="I78" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79">
@@ -4410,13 +4470,13 @@
         <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4426,27 +4486,27 @@
         <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>49</v>
+        <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>175</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>281</v>
+        <v>118</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
@@ -4456,21 +4516,21 @@
         <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>311</v>
+        <v>177</v>
       </c>
       <c r="J80" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="C81" s="3" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>44</v>
@@ -4483,34 +4543,32 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>214</v>
+        <v>118</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>315</v>
-      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
@@ -4518,10 +4576,10 @@
         <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -4532,13 +4590,13 @@
         <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>44</v>
+        <v>235</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
@@ -4548,10 +4606,10 @@
         <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -4562,13 +4620,13 @@
         <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4578,10 +4636,10 @@
         <v>322</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -4589,70 +4647,74 @@
         <v>323</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>325</v>
+        <v>149</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="J85" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>328</v>
+        <v>140</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>329</v>
+        <v>56</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>332</v>
+        <v>218</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>44</v>
@@ -4665,27 +4727,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>147</v>
+        <v>332</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>45</v>
@@ -4695,10 +4757,10 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4706,45 +4768,43 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>240</v>
-      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="J89" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>118</v>
@@ -4757,83 +4817,83 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>197</v>
+        <v>335</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>343</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="J91" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>346</v>
+        <v>301</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>159</v>
+        <v>302</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>44</v>
+        <v>303</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="J92" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>56</v>
@@ -4849,17 +4909,201 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I93" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J93" s="3">
-        <v>48</v>
+      <c r="I94" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J96" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J97" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J98" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J99" s="3">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4953,6 +5197,12 @@
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4960,9 +5210,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4994,13 +5244,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5008,7 +5258,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -5016,10 +5266,10 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5027,18 +5277,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5046,18 +5296,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>234</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5065,18 +5315,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5084,18 +5334,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5103,18 +5353,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5122,18 +5372,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>159</v>
+        <v>313</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5141,18 +5391,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5160,18 +5410,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>258</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>156</v>
+        <v>332</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5179,18 +5429,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>260</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5198,18 +5448,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5217,18 +5467,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>147</v>
+        <v>349</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5236,30 +5486,11 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5274,7 +5505,6 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5288,23 +5518,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>240</v>
+        <v>141</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5312,7 +5542,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5320,15 +5550,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5336,7 +5566,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5344,15 +5574,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5360,7 +5590,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5368,7 +5598,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>315</v>
+        <v>373</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5376,7 +5606,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -5392,7 +5622,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5400,7 +5630,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5408,7 +5638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5421,7 +5651,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5430,7 +5660,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -5451,7 +5681,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5459,15 +5689,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5475,7 +5705,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5483,7 +5713,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5491,7 +5721,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5499,7 +5729,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5507,7 +5737,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5515,7 +5745,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5523,7 +5753,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5531,7 +5761,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5539,7 +5769,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5547,7 +5777,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>272</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5561,23 +5791,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -5669,7 +5899,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C8" s="3">
         <v>4.6</v>
@@ -5683,13 +5913,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5697,10 +5927,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="C10" s="3">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5711,7 +5941,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>212</v>
+        <v>301</v>
       </c>
       <c r="C11" s="3">
         <v>3.1</v>
@@ -5739,7 +5969,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5753,7 +5983,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5767,13 +5997,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5781,13 +6011,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5807,15 +6037,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -5829,10 +6059,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
@@ -5840,10 +6070,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -5862,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -5878,7 +6108,7 @@
         <v>118</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -5891,7 +6121,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5899,23 +6129,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>303</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5923,7 +6153,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5938,7 +6168,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5950,10 +6180,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5965,10 +6195,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5985,31 +6215,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
@@ -6017,31 +6247,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>211</v>
+        <v>300</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>212</v>
+        <v>301</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>213</v>
+        <v>302</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>215</v>
+        <v>304</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>216</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -6049,31 +6279,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F4" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -6081,31 +6311,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F5" s="3">
         <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6">
@@ -6113,31 +6343,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>139</v>
+        <v>405</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>388</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7">
@@ -6145,31 +6375,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>392</v>
+        <v>149</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -6177,31 +6407,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>382</v>
-      </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>399</v>
+        <v>347</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
@@ -6209,28 +6439,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="F9" s="3">
         <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>86</v>
@@ -6241,31 +6471,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F10" s="3">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
@@ -6273,31 +6503,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>127</v>
+        <v>427</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>86</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12">
@@ -6305,31 +6535,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>411</v>
+        <v>127</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>413</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -6346,13 +6576,13 @@
         <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F13" s="3">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
@@ -6369,31 +6599,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15">
@@ -6401,31 +6631,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>377</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -6433,31 +6663,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>427</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
@@ -6465,31 +6695,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>397</v>
+        <v>448</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>159</v>
+        <v>449</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>150</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18">
@@ -6497,31 +6727,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>159</v>
+        <v>455</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
@@ -6529,31 +6759,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>159</v>
+        <v>332</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20">
@@ -6561,31 +6791,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>317</v>
+        <v>462</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21">
@@ -6593,31 +6823,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>448</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W29.xlsx
+++ b/reports/devops-jobs-israel-2026-W29.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-15T08:29:35</t>
+    <t xml:space="preserve">2026-07-16T08:27:25</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -438,711 +438,735 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4440994599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software AG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36900-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439717780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4441420450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-infinidat-4437658931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubeus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kubeus-4438456773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harel Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4438480442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeerSpot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinecone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4438051951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4438489425</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA AI</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4437214837</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
+    <t xml:space="preserve">Cloud engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataspan.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4438467479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4440042602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-05</t>
   </si>
   <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Infrastructure Engineer - Chip Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-infrastructure-engineer-chip-design-at-nvidia-ai-4438465890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4431766041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freelance DevOps IT Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeteorOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/freelance-devops-it-engineer-at-meteorops-4438098835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belocal Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4440002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4438417196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security &amp; Cloud Engineers | Multiple Open Positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nanosek Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-cloud-engineers-multiple-open-positions-at-nanosek-ltd-4438482517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Lead</t>
   </si>
   <si>
     <t xml:space="preserve">Bagira</t>
   </si>
   <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
   </si>
   <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AM Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harel Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeerSpot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4438051951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobscroller-4438942609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36900-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439717780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4438598493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Facing System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarity Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4435649753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4437678341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python Infrastructure Engineer</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belocal Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4439138209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (36856)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-36856-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439722636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4436692890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4437215091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
@@ -1167,10 +1191,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9%</t>
+    <t xml:space="preserve">54.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1182,6 +1206,12 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -1200,12 +1230,6 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -1224,6 +1248,15 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
   </si>
   <si>
@@ -1233,22 +1266,19 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
@@ -1287,9 +1317,6 @@
     <t xml:space="preserve">Camtek</t>
   </si>
   <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1299,6 +1326,18 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -1311,7 +1350,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-30</t>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
@@ -1320,115 +1371,43 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+    <t xml:space="preserve">Segment IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-segment-it-4438049762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1604,7 +1583,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1612,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1620,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -1628,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>981</v>
+        <v>997</v>
       </c>
     </row>
     <row r="10">
@@ -1700,7 +1679,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1727,28 +1706,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1756,7 +1735,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1764,7 +1743,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1783,130 +1762,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>471</v>
+        <v>369</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>343</v>
+        <v>465</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>260</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>326</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>476</v>
+        <v>377</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1931,13 +1910,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2">
@@ -1948,10 +1927,10 @@
         <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>13.1</v>
+        <v>20.7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1960,88 +1939,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
-        <v>32.7</v>
+        <v>31.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.6</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>37.7</v>
+        <v>33.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2054,7 +2033,7 @@
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2125,7 +2104,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -2157,7 +2136,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2189,7 +2168,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -2221,7 +2200,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -2253,7 +2232,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -2285,7 +2264,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -2317,7 +2296,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -2349,7 +2328,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -2381,7 +2360,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -2413,7 +2392,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2445,7 +2424,7 @@
         <v>72</v>
       </c>
       <c r="J12" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -2477,7 +2456,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2488,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2541,7 +2520,7 @@
         <v>96</v>
       </c>
       <c r="J15" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2573,7 +2552,7 @@
         <v>79</v>
       </c>
       <c r="J16" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -2605,7 +2584,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -2637,7 +2616,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -2669,7 +2648,7 @@
         <v>111</v>
       </c>
       <c r="J19" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -2701,7 +2680,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -2733,7 +2712,7 @@
         <v>121</v>
       </c>
       <c r="J21" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -2765,7 +2744,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
@@ -2797,7 +2776,7 @@
         <v>131</v>
       </c>
       <c r="J23" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -2829,7 +2808,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -2861,39 +2840,37 @@
         <v>79</v>
       </c>
       <c r="J25" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27">
@@ -2901,13 +2878,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>45</v>
@@ -2917,13 +2894,13 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2931,10 +2908,10 @@
         <v>112</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2947,13 +2924,13 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J28" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2961,13 +2938,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2980,10 +2957,10 @@
         <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="J29" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3013,7 +2990,7 @@
         <v>86</v>
       </c>
       <c r="J30" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31">
@@ -3024,26 +3001,26 @@
         <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J31" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -3051,10 +3028,10 @@
         <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>44</v>
@@ -3067,10 +3044,10 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J32" s="3">
         <v>1</v>
@@ -3078,16 +3055,16 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3097,18 +3074,18 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="J33" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>170</v>
@@ -3130,10 +3107,10 @@
         <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -3141,13 +3118,13 @@
         <v>112</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>45</v>
@@ -3157,120 +3134,120 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J36" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="J37" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3280,27 +3257,27 @@
         <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="J39" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3310,21 +3287,21 @@
         <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="J40" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="C41" s="3" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>44</v>
@@ -3332,9 +3309,7 @@
       <c r="E41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
@@ -3345,21 +3320,21 @@
         <v>197</v>
       </c>
       <c r="J41" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>45</v>
@@ -3369,62 +3344,64 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="J42" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
@@ -3432,21 +3409,21 @@
         <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
@@ -3459,54 +3436,54 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="J45" s="3">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>42</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>44</v>
@@ -3515,60 +3492,60 @@
         <v>45</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="J47" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>49</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
@@ -3581,116 +3558,114 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="J51" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>44</v>
@@ -3703,30 +3678,30 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3736,24 +3711,24 @@
         <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>235</v>
+        <v>44</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3763,30 +3738,30 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>237</v>
+        <v>49</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
@@ -3796,21 +3771,21 @@
         <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>44</v>
@@ -3826,37 +3801,37 @@
         <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J58" s="3">
         <v>2</v>
@@ -3867,10 +3842,10 @@
         <v>49</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>44</v>
@@ -3883,40 +3858,40 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="J59" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J60" s="3">
         <v>1</v>
@@ -3924,16 +3899,16 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3943,10 +3918,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3954,79 +3929,81 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>49</v>
+        <v>257</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>258</v>
+        <v>151</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="J63" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
@@ -4036,27 +4013,27 @@
         <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="J64" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>185</v>
+        <v>262</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
@@ -4066,10 +4043,10 @@
         <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
@@ -4080,13 +4057,13 @@
         <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
@@ -4096,10 +4073,10 @@
         <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="J66" s="3">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4110,7 +4087,7 @@
         <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
@@ -4126,84 +4103,84 @@
         <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="J68" s="3">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>275</v>
+        <v>49</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>149</v>
+        <v>282</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
@@ -4213,27 +4190,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="J70" s="3">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>118</v>
+        <v>278</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>45</v>
@@ -4243,100 +4220,100 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>162</v>
+        <v>287</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>112</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>208</v>
+        <v>144</v>
       </c>
       <c r="J73" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>278</v>
+        <v>173</v>
       </c>
       <c r="J74" s="3">
         <v>3</v>
@@ -4344,49 +4321,49 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>151</v>
+        <v>295</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>293</v>
+        <v>140</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="J75" s="3">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>295</v>
+        <v>112</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>296</v>
+        <v>158</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
@@ -4396,27 +4373,27 @@
         <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>278</v>
+        <v>160</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
@@ -4426,54 +4403,54 @@
         <v>299</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>208</v>
+        <v>144</v>
       </c>
       <c r="J77" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="E78" s="3" t="s">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="I78" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="J78" s="3">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>118</v>
+        <v>302</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>45</v>
@@ -4486,7 +4463,7 @@
         <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J79" s="3">
         <v>2</v>
@@ -4497,16 +4474,16 @@
         <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>175</v>
+        <v>292</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
@@ -4516,10 +4493,10 @@
         <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="J80" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4530,10 +4507,10 @@
         <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>45</v>
@@ -4543,57 +4520,57 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J82" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
@@ -4603,30 +4580,30 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>235</v>
+        <v>151</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4636,39 +4613,37 @@
         <v>322</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>216</v>
+        <v>323</v>
       </c>
       <c r="J84" s="3">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4676,13 +4651,13 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>44</v>
@@ -4691,33 +4666,33 @@
         <v>45</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>326</v>
+        <v>204</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>216</v>
+        <v>329</v>
       </c>
       <c r="J86" s="3">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>56</v>
+        <v>332</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>45</v>
@@ -4727,27 +4702,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>147</v>
+        <v>334</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>208</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>332</v>
+        <v>56</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>45</v>
@@ -4757,24 +4732,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>118</v>
@@ -4787,24 +4762,24 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>118</v>
@@ -4817,24 +4792,24 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>118</v>
@@ -4847,10 +4822,10 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4858,48 +4833,46 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="C92" s="3" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>303</v>
+        <v>118</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>343</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>56</v>
+        <v>351</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>45</v>
@@ -4909,27 +4882,27 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>349</v>
+        <v>56</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>45</v>
@@ -4939,119 +4912,119 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>354</v>
+        <v>195</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="J96" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>356</v>
+        <v>179</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>278</v>
+        <v>86</v>
       </c>
       <c r="J97" s="3">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>303</v>
+        <v>118</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>38</v>
@@ -5061,24 +5034,24 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="J98" s="3">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>362</v>
+        <v>227</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>206</v>
+        <v>366</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>44</v>
@@ -5086,24 +5059,84 @@
       <c r="E99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>363</v>
-      </c>
+      <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I99" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I100" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J99" s="3">
-        <v>47</v>
+      <c r="J100" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J101" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J101"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5203,6 +5236,8 @@
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5210,9 +5245,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="1" max="1" width="55" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5244,10 +5279,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>56</v>
@@ -5258,7 +5293,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -5266,10 +5301,10 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5277,18 +5312,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5296,18 +5331,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5315,18 +5350,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>237</v>
+        <v>153</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5334,18 +5369,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>249</v>
+        <v>112</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5353,18 +5388,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>264</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5372,18 +5407,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>313</v>
+        <v>140</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5391,18 +5426,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>323</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>149</v>
+        <v>282</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5410,18 +5445,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>332</v>
+        <v>140</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5429,18 +5464,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>334</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>171</v>
+        <v>298</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5448,18 +5483,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5467,18 +5502,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>349</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5486,11 +5521,68 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>350</v>
       </c>
+      <c r="C16" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>357</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5505,6 +5597,9 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5518,23 +5613,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5542,7 +5637,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5550,7 +5645,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5558,7 +5653,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5566,7 +5661,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5574,15 +5669,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>326</v>
+        <v>379</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5590,7 +5685,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5598,7 +5693,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>373</v>
+        <v>260</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5606,7 +5701,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -5622,7 +5717,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5630,7 +5725,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5638,7 +5733,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5660,7 +5755,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5681,7 +5776,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5689,23 +5784,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5713,7 +5808,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5721,7 +5816,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5729,7 +5824,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5737,7 +5832,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5753,7 +5848,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5761,7 +5856,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5769,7 +5864,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5777,7 +5872,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5798,16 +5893,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5899,7 +5994,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C8" s="3">
         <v>4.6</v>
@@ -5913,13 +6008,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="C9" s="3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5927,13 +6022,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>140</v>
+        <v>292</v>
       </c>
       <c r="C10" s="3">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5941,10 +6036,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5955,13 +6050,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>258</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5969,13 +6064,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5983,7 +6078,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5997,7 +6092,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -6037,15 +6132,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -6059,10 +6154,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -6073,7 +6168,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6092,7 +6187,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -6100,7 +6195,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -6116,12 +6211,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6129,7 +6224,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6137,7 +6232,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6153,7 +6248,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6180,10 +6275,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6195,10 +6290,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6215,31 +6310,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>387</v>
+        <v>321</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>388</v>
+        <v>258</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>392</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3">
@@ -6247,31 +6342,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>305</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
@@ -6279,31 +6374,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5">
@@ -6311,31 +6406,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>151</v>
+        <v>409</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>293</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>403</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -6343,31 +6438,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>407</v>
-      </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>169</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7">
@@ -6375,31 +6470,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>335</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>411</v>
+        <v>208</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F7" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8">
@@ -6407,31 +6502,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>345</v>
+        <v>416</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>346</v>
+        <v>210</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="F8" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9">
@@ -6439,31 +6534,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="F9" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -6471,31 +6566,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>420</v>
+        <v>349</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>422</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F10" s="3">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>425</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -6509,13 +6604,13 @@
         <v>427</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F11" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>428</v>
@@ -6527,7 +6622,7 @@
         <v>429</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>430</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -6535,31 +6630,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>127</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>128</v>
+        <v>332</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>86</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13">
@@ -6567,31 +6662,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>349</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>435</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F13" s="3">
         <v>56</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>61</v>
+        <v>437</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>62</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14">
@@ -6599,28 +6694,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>438</v>
@@ -6631,31 +6726,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>164</v>
+        <v>444</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>75</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16">
@@ -6663,31 +6758,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>444</v>
+        <v>127</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>147</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -6695,22 +6790,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F17" s="3">
+        <v>47</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F17" s="3">
-        <v>30</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
@@ -6719,7 +6814,7 @@
         <v>451</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>452</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18">
@@ -6727,31 +6822,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>453</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>454</v>
+        <v>55</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>455</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F18" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>457</v>
+        <v>61</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>200</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -6759,31 +6854,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>395</v>
+        <v>349</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>332</v>
+        <v>199</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>461</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20">
@@ -6791,31 +6886,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>463</v>
+        <v>342</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>438</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21">
@@ -6823,31 +6918,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>216</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W29.xlsx
+++ b/reports/devops-jobs-israel-2026-W29.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-16T08:27:25</t>
+    <t xml:space="preserve">2026-07-17T08:23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0%</t>
+    <t xml:space="preserve">1.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -240,15 +240,6 @@
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Director of Platform Security</t>
   </si>
   <si>
@@ -447,6 +438,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4438744313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4441125336</t>
+  </si>
+  <si>
     <t xml:space="preserve">CommBox</t>
   </si>
   <si>
@@ -504,6 +516,15 @@
     <t xml:space="preserve">2026-06-23</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
   </si>
   <si>
@@ -513,6 +534,300 @@
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
+    <t xml:space="preserve">HISKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4441902997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oak - Identity Security OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-oak-identity-security-os-4441447115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4438480442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4438051951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeerSpot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinecone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
   </si>
   <si>
@@ -528,777 +843,525 @@
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer (36900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36900-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439717780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4438467479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Junior</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4441420450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4438720709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harel Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataspan.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
   </si>
   <si>
     <t xml:space="preserve">WalkMe</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438772693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4441455597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belocal Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4438414159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4439138209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4440002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead System Engineer, R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectrum Dynamics Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-system-engineer-r-d-at-spectrum-dynamics-medical-4437647939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4438417196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kafka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
     <t xml:space="preserve">Radware</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AM Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-devops-engineer-at-am-consulting-4437215331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubeus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kubeus-4438456773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harel Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4438480442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeerSpot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinecone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4438051951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4438489425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4437214837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataspan.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4438467479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Infrastructure Engineer - Chip Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-infrastructure-engineer-chip-design-at-nvidia-ai-4438465890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4431766041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freelance DevOps IT Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MeteorOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/freelance-devops-it-engineer-at-meteorops-4438098835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belocal Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4440002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4438417196</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
   </si>
   <si>
     <t xml:space="preserve">Allpha Innovation</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
   </si>
   <si>
-    <t xml:space="preserve">Security &amp; Cloud Engineers | Multiple Open Positions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nanosek Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-cloud-engineers-multiple-open-positions-at-nanosek-ltd-4438482517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1326,30 +1389,45 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
     <t xml:space="preserve">eToro</t>
   </si>
   <si>
@@ -1380,15 +1458,6 @@
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Segment IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-segment-it-4438049762</t>
-  </si>
-  <si>
     <t xml:space="preserve">L3 Support Engineer</t>
   </si>
   <si>
@@ -1398,33 +1467,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
@@ -1432,6 +1489,9 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1583,7 +1643,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
@@ -1591,7 +1651,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1599,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1607,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>997</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10">
@@ -1615,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1679,7 +1739,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -1687,7 +1747,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1706,12 +1766,12 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="B2" s="3">
         <v>36</v>
@@ -1719,23 +1779,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1743,7 +1803,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1762,39 +1822,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B5" s="3">
         <v>26</v>
@@ -1802,7 +1862,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>260</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3">
         <v>25</v>
@@ -1810,23 +1870,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>467</v>
+        <v>394</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>381</v>
+        <v>487</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
@@ -1834,31 +1894,31 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>377</v>
+        <v>488</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>469</v>
+        <v>390</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>470</v>
+        <v>388</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>374</v>
+        <v>489</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -1866,15 +1926,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>375</v>
+        <v>490</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1882,10 +1942,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1910,13 +1970,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2">
@@ -1924,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>20.7</v>
+        <v>12.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1939,88 +1999,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3">
-        <v>31.6</v>
+        <v>36.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.5</v>
+        <v>28.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.0</v>
+        <v>19.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2033,7 +2093,7 @@
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2104,7 +2164,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -2136,7 +2196,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -2168,7 +2228,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -2200,7 +2260,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -2232,7 +2292,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -2264,7 +2324,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -2296,7 +2356,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -2328,12 +2388,12 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>69</v>
@@ -2348,24 +2408,24 @@
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>69</v>
@@ -2380,19 +2440,19 @@
         <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="J11" s="3">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -2421,21 +2481,21 @@
         <v>82</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>44</v>
@@ -2444,30 +2504,30 @@
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J13" s="3">
-        <v>62</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>44</v>
@@ -2476,30 +2536,30 @@
         <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>44</v>
@@ -2508,30 +2568,30 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="J15" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>44</v>
@@ -2540,68 +2600,68 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="J16" s="3">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>106</v>
@@ -2613,117 +2673,117 @@
         <v>107</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="J18" s="3">
-        <v>65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>11</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="J20" s="3">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>44</v>
@@ -2732,30 +2792,30 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>44</v>
@@ -2764,19 +2824,19 @@
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
@@ -2784,10 +2844,10 @@
         <v>132</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>44</v>
@@ -2796,56 +2856,54 @@
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="J24" s="3">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>138</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J25" s="3">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>139</v>
@@ -2854,7 +2912,7 @@
         <v>140</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>45</v>
@@ -2867,24 +2925,24 @@
         <v>141</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="J26" s="3">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>45</v>
@@ -2894,10 +2952,10 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -2905,13 +2963,13 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2930,12 +2988,12 @@
         <v>148</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>149</v>
@@ -2944,7 +3002,7 @@
         <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>45</v>
@@ -2954,27 +3012,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -2987,10 +3045,10 @@
         <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="J30" s="3">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3001,10 +3059,10 @@
         <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -3014,27 +3072,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="J31" s="3">
-        <v>23</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>45</v>
@@ -3044,18 +3102,18 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>165</v>
@@ -3064,7 +3122,7 @@
         <v>166</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3077,24 +3135,24 @@
         <v>167</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>45</v>
@@ -3104,27 +3162,27 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J34" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>45</v>
@@ -3134,84 +3192,84 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="J35" s="3">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>44</v>
@@ -3224,40 +3282,40 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -3265,16 +3323,16 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>45</v>
@@ -3284,10 +3342,10 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -3295,13 +3353,13 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>44</v>
@@ -3309,32 +3367,34 @@
       <c r="E41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="J41" s="3">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>45</v>
@@ -3344,146 +3404,144 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="I44" s="3" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="J44" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>207</v>
+        <v>49</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>44</v>
@@ -3491,34 +3549,32 @@
       <c r="E47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>204</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="J47" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>45</v>
@@ -3534,7 +3590,7 @@
         <v>218</v>
       </c>
       <c r="J48" s="3">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
@@ -3545,10 +3601,10 @@
         <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>45</v>
@@ -3561,21 +3617,21 @@
         <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>44</v>
@@ -3588,30 +3644,30 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
@@ -3621,24 +3677,24 @@
         <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>38</v>
@@ -3648,30 +3704,30 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>56</v>
+        <v>188</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3681,24 +3737,24 @@
         <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>49</v>
+        <v>232</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>38</v>
@@ -3708,24 +3764,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="J54" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
@@ -3738,54 +3794,54 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>44</v>
@@ -3798,24 +3854,24 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="J57" s="3">
-        <v>23</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>242</v>
+        <v>109</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
@@ -3828,24 +3884,24 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>44</v>
@@ -3858,57 +3914,57 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>249</v>
+        <v>188</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>44</v>
+        <v>255</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3918,27 +3974,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>144</v>
+        <v>257</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3948,45 +4004,43 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="J62" s="3">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>260</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -3994,13 +4048,13 @@
         <v>49</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4010,27 +4064,27 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="J64" s="3">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>265</v>
+        <v>52</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>174</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
@@ -4040,27 +4094,27 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="J65" s="3">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>171</v>
+        <v>271</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>45</v>
@@ -4070,57 +4124,57 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>163</v>
+        <v>273</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>140</v>
+        <v>234</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4130,27 +4184,27 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="J68" s="3">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>277</v>
+        <v>150</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>278</v>
+        <v>44</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>38</v>
@@ -4160,60 +4214,60 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>280</v>
+        <v>152</v>
       </c>
       <c r="J69" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>49</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>139</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>277</v>
+        <v>140</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>278</v>
+        <v>115</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
@@ -4223,27 +4277,27 @@
         <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -4253,24 +4307,24 @@
         <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>290</v>
+        <v>162</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>45</v>
@@ -4283,37 +4337,37 @@
         <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>245</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="J74" s="3">
         <v>3</v>
@@ -4321,46 +4375,46 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>295</v>
+        <v>143</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>158</v>
+        <v>296</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>45</v>
@@ -4373,54 +4427,54 @@
         <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="J76" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>292</v>
+        <v>214</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="I77" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>112</v>
+        <v>300</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>301</v>
+        <v>176</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>302</v>
+        <v>44</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>45</v>
@@ -4430,43 +4484,43 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="J78" s="3">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="D79" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80">
@@ -4474,26 +4528,28 @@
         <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>140</v>
+        <v>311</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J80" s="3">
         <v>0</v>
@@ -4501,16 +4557,16 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>307</v>
+        <v>150</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>302</v>
+        <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>45</v>
@@ -4520,24 +4576,24 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>234</v>
+        <v>152</v>
       </c>
       <c r="J81" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>316</v>
+        <v>137</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>44</v>
@@ -4550,87 +4606,87 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>183</v>
+        <v>322</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J84" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>324</v>
+        <v>109</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>329</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>45</v>
@@ -4640,10 +4696,10 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4651,48 +4707,46 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>327</v>
+        <v>49</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>204</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J86" s="3">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>330</v>
+        <v>109</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>332</v>
+        <v>176</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>45</v>
@@ -4702,13 +4756,13 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>334</v>
+        <v>142</v>
       </c>
       <c r="J87" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4716,10 +4770,10 @@
         <v>335</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>208</v>
+        <v>336</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>44</v>
@@ -4727,62 +4781,66 @@
       <c r="E88" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>337</v>
+        <v>42</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>339</v>
+        <v>137</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>163</v>
+        <v>295</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>342</v>
+        <v>211</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>45</v>
@@ -4792,27 +4850,27 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>282</v>
+        <v>172</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>45</v>
@@ -4822,27 +4880,27 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>45</v>
@@ -4852,27 +4910,27 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>351</v>
+        <v>188</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>45</v>
@@ -4882,10 +4940,10 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J93" s="3">
         <v>0</v>
@@ -4893,78 +4951,76 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>148</v>
+        <v>273</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>204</v>
-      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>195</v>
+        <v>356</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>45</v>
@@ -4974,27 +5030,27 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="J96" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>44</v>
+        <v>216</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>38</v>
@@ -5004,73 +5060,73 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="J97" s="3">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="D98" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J98" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>227</v>
+        <v>348</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I99" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="I99" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J99" s="3">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
@@ -5078,65 +5134,155 @@
         <v>368</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>195</v>
+        <v>369</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>179</v>
+        <v>370</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>369</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>96</v>
+        <v>372</v>
       </c>
       <c r="J100" s="3">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>227</v>
+        <v>373</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>179</v>
+        <v>305</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F101" s="3"/>
+      <c r="F101" s="3" t="s">
+        <v>374</v>
+      </c>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="I101" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J101" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I102" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J101" s="3">
-        <v>2</v>
+      <c r="J102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J103" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J104" s="3">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
+  <autoFilter ref="A1:J104"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5238,6 +5384,9 @@
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5245,9 +5394,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="55" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5279,13 +5428,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5293,18 +5442,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5312,18 +5461,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5331,18 +5480,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5350,18 +5499,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5369,18 +5518,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5388,18 +5537,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5407,18 +5556,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>246</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5426,18 +5575,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5445,18 +5594,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>309</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>140</v>
+        <v>311</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5464,18 +5613,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5483,18 +5632,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>309</v>
+        <v>109</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5502,18 +5651,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5521,18 +5670,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>282</v>
+        <v>360</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5540,49 +5689,11 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5598,8 +5709,6 @@
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5613,47 +5722,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>377</v>
+        <v>312</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5661,71 +5770,71 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>374</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5733,7 +5842,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5755,7 +5864,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5763,7 +5872,7 @@
         <v>69</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -5776,7 +5885,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5784,23 +5893,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>292</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5808,7 +5917,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5816,7 +5925,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5824,7 +5933,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5832,7 +5941,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5840,7 +5949,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5848,7 +5957,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5856,7 +5965,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5864,7 +5973,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5872,7 +5981,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5893,16 +6002,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5910,13 +6019,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3">
-        <v>19.2</v>
+        <v>10.9</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5924,13 +6033,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5938,7 +6047,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3">
         <v>6.7</v>
@@ -5952,7 +6061,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" s="3">
         <v>5.3</v>
@@ -5966,7 +6075,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C6" s="3">
         <v>5.0</v>
@@ -5994,10 +6103,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="C8" s="3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
@@ -6008,13 +6117,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6022,13 +6131,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6036,13 +6145,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C11" s="3">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6050,10 +6159,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>258</v>
+        <v>139</v>
       </c>
       <c r="C12" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -6064,13 +6173,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>220</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6078,7 +6187,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6092,13 +6201,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>288</v>
+        <v>120</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6106,13 +6215,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6132,18 +6241,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>306</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6154,10 +6263,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4">
@@ -6165,10 +6274,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -6187,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
@@ -6195,20 +6304,20 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>155</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6216,31 +6325,31 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>302</v>
+        <v>102</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6248,10 +6357,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6275,10 +6384,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6290,10 +6399,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6310,31 +6419,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
@@ -6342,31 +6451,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4">
@@ -6374,31 +6483,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>408</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
@@ -6406,31 +6515,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
@@ -6438,31 +6547,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>262</v>
+        <v>144</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F6" s="3">
         <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7">
@@ -6470,31 +6579,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F7" s="3">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>336</v>
+        <v>427</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>163</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8">
@@ -6502,31 +6611,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>210</v>
+        <v>429</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>140</v>
+        <v>430</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>163</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -6534,31 +6643,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="F9" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -6566,31 +6675,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>349</v>
+        <v>440</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="F10" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -6598,31 +6707,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12">
@@ -6630,31 +6739,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>434</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -6662,31 +6771,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>349</v>
+        <v>451</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>171</v>
+        <v>370</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F13" s="3">
         <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14">
@@ -6694,31 +6803,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15">
@@ -6726,31 +6835,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>443</v>
+        <v>143</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>444</v>
+        <v>144</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F15" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>447</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16">
@@ -6758,31 +6867,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>127</v>
+        <v>465</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>86</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17">
@@ -6790,31 +6899,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>264</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18">
@@ -6822,31 +6931,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>435</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>61</v>
+        <v>475</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -6854,31 +6963,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>349</v>
+        <v>435</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>163</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20">
@@ -6886,31 +6995,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>456</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>342</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>458</v>
+        <v>61</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -6918,31 +7027,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>460</v>
+        <v>342</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="F21" s="3">
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W29.xlsx
+++ b/reports/devops-jobs-israel-2026-W29.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-17T08:23:14</t>
+    <t xml:space="preserve">2026-07-19T08:29:57</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0%</t>
+    <t xml:space="preserve">1.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -429,517 +429,664 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-infinidat-4437658931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4437214837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harel Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4438744313</t>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4440994599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software AG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-17</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nexxen-4441765768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4441985184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeerSpot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freelance DevOps IT Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeteorOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/freelance-devops-it-engineer-at-meteorops-4438098835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps and Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceragon Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-linux-administrator-at-ceragon-networks-4438717983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4438480442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinecone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
   </si>
   <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4441125336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4440994599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software AG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4438486047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4441457552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentrycs | Counter-Drone Solutions Adapting at the Speed of Threats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentrycs-counter-drone-solutions-adapting-at-the-speed-of-threats-4440549024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-hisky-4440085665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4437267071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of QA Automation and DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-qa-automation-and-devops-at-genpact-4439655949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4440223220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-ai-platform-engineer-at-armis-4422925341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4440002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4439138209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead System Engineer, R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectrum Dynamics Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-system-engineer-r-d-at-spectrum-dynamics-medical-4437647939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Team Lead</t>
   </si>
   <si>
-    <t xml:space="preserve">Capitolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-capitolis-4441445229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4440962651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4441465768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4441902997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oak - Identity Security OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-oak-identity-security-os-4441447115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGO NEXT Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4438480442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4438051951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 239442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-israel-4437219161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yad2-4440006607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-infrastructure-engineer-at-evoke-4437676981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Infrastructure &amp; Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeerSpot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-infrastructure-platform-at-peerspot-4440826501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinecone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-site-reliability-engineer-at-pinecone-4441277238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
   </si>
   <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4437254187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4438706492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4438096276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-antidote-health-4439198034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4437277427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4438467479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4437647743</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4433116067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kafka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
   </si>
   <si>
     <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
@@ -948,523 +1095,229 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4438720709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harel Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-llm-at-harel-finance-4437265914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataspan.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems and Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-and-cloud-infrastructure-engineer-at-logica-it-4437679372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-leidos-4438772693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4422598024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4441455597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belocal Ltd</t>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4438720783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4440575333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-belocal-ltd-4437657603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4438414159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4439138209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4440002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead System Engineer, R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spectrum Dynamics Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-system-engineer-r-d-at-spectrum-dynamics-medical-4437647939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4438417196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4441499292</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1473,25 +1326,22 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1643,7 +1493,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -1651,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1659,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1667,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1011</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="10">
@@ -1739,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -1766,20 +1616,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -1787,15 +1637,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>412</v>
+        <v>358</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1803,7 +1653,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1822,119 +1672,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>482</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>483</v>
+        <v>337</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>484</v>
+        <v>216</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>485</v>
+        <v>435</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>374</v>
+        <v>436</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>486</v>
+        <v>438</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>487</v>
+        <v>339</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>488</v>
+        <v>439</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>390</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>489</v>
+        <v>331</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>490</v>
+        <v>332</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1942,10 +1792,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>393</v>
+        <v>335</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1970,13 +1820,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>491</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>492</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>493</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -1987,10 +1837,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1999,19 +1849,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3">
-        <v>36.1</v>
+        <v>34.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>495</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -2020,67 +1870,67 @@
         <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>496</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>497</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>498</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.7</v>
+        <v>66.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>499</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2164,7 +2014,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -2196,7 +2046,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -2228,7 +2078,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -2260,7 +2110,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -2292,7 +2142,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2324,7 +2174,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -2356,7 +2206,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -2388,7 +2238,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -2420,7 +2270,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -2452,7 +2302,7 @@
         <v>72</v>
       </c>
       <c r="J11" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -2484,7 +2334,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -2516,7 +2366,7 @@
         <v>89</v>
       </c>
       <c r="J13" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -2548,7 +2398,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -2580,7 +2430,7 @@
         <v>76</v>
       </c>
       <c r="J15" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -2612,7 +2462,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -2644,7 +2494,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -2676,7 +2526,7 @@
         <v>108</v>
       </c>
       <c r="J18" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2708,7 +2558,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2740,7 +2590,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -2772,7 +2622,7 @@
         <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -2804,7 +2654,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -2836,7 +2686,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
@@ -2868,21 +2718,21 @@
         <v>76</v>
       </c>
       <c r="J24" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>45</v>
@@ -2892,43 +2742,45 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="J25" s="3">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2936,13 +2788,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>45</v>
@@ -2952,13 +2804,13 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2966,10 +2818,10 @@
         <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2982,24 +2834,24 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>44</v>
@@ -3012,13 +2864,13 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J29" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3026,13 +2878,13 @@
         <v>109</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>45</v>
@@ -3042,27 +2894,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -3075,21 +2927,21 @@
         <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J31" s="3">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>115</v>
@@ -3105,10 +2957,10 @@
         <v>163</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="J32" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -3116,13 +2968,13 @@
         <v>109</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3132,13 +2984,13 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3146,10 +2998,10 @@
         <v>109</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>44</v>
@@ -3162,13 +3014,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="J34" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3176,13 +3028,13 @@
         <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>45</v>
@@ -3192,10 +3044,10 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J35" s="3">
         <v>3</v>
@@ -3203,103 +3055,103 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
@@ -3312,27 +3164,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>45</v>
@@ -3342,34 +3194,32 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
@@ -3377,21 +3227,21 @@
         <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="J41" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
@@ -3404,87 +3254,87 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J42" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>38</v>
@@ -3497,10 +3347,10 @@
         <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3508,29 +3358,31 @@
         <v>207</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47">
@@ -3541,10 +3393,10 @@
         <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>45</v>
@@ -3557,10 +3409,10 @@
         <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3574,12 +3426,14 @@
         <v>215</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F48" s="3"/>
+      <c r="F48" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
@@ -3587,54 +3441,54 @@
         <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="J48" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>219</v>
+        <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>45</v>
@@ -3647,7 +3501,7 @@
         <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="J50" s="3">
         <v>2</v>
@@ -3655,43 +3509,43 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J51" s="3">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>44</v>
@@ -3704,57 +3558,57 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>38</v>
@@ -3764,27 +3618,27 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3794,24 +3648,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
@@ -3824,54 +3678,56 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J56" s="3">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="J57" s="3">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>109</v>
+        <v>249</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
@@ -3884,10 +3740,10 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="J58" s="3">
         <v>4</v>
@@ -3895,16 +3751,16 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>248</v>
+        <v>159</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>137</v>
+        <v>252</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3914,27 +3770,27 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>76</v>
+        <v>254</v>
       </c>
       <c r="J59" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>45</v>
@@ -3944,10 +3800,10 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -3955,16 +3811,16 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>49</v>
+        <v>260</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>255</v>
+        <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3974,27 +3830,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>257</v>
+        <v>156</v>
       </c>
       <c r="J61" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>259</v>
+        <v>150</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -4004,27 +3860,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>255</v>
+        <v>44</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>45</v>
@@ -4034,207 +3890,207 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>49</v>
+        <v>269</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>137</v>
+        <v>271</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="J64" s="3">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>52</v>
+        <v>273</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="J65" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>269</v>
+        <v>49</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>271</v>
+        <v>150</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="J66" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="J68" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>179</v>
+        <v>286</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>44</v>
+        <v>289</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>282</v>
+        <v>109</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>45</v>
@@ -4244,84 +4100,84 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>49</v>
+        <v>292</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>139</v>
+        <v>293</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>140</v>
+        <v>294</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>290</v>
+        <v>197</v>
       </c>
       <c r="J72" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>162</v>
+        <v>299</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>115</v>
@@ -4334,27 +4190,27 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="J73" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>176</v>
+        <v>303</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>44</v>
+        <v>289</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
@@ -4364,54 +4220,54 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>143</v>
+        <v>297</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>115</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>295</v>
+        <v>140</v>
       </c>
       <c r="J75" s="3">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>166</v>
+        <v>308</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>115</v>
@@ -4424,10 +4280,10 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="J76" s="3">
         <v>4</v>
@@ -4435,16 +4291,16 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>214</v>
+        <v>310</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>45</v>
@@ -4454,162 +4310,160 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>299</v>
+        <v>209</v>
       </c>
       <c r="J77" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>290</v>
+        <v>166</v>
       </c>
       <c r="J78" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="J79" s="3">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>311</v>
+        <v>170</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>312</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>314</v>
+        <v>200</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="J82" s="3">
         <v>5</v>
@@ -4617,672 +4471,36 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>322</v>
+        <v>190</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="J84" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J86" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J88" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="J89" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J90" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J91" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J92" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="J94" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J95" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J98" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="J99" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="J100" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J101" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J102" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J103" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J104" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
+  <autoFilter ref="A1:J83"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5366,27 +4584,6 @@
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
-    <hyperlink ref="H84" r:id="rId83"/>
-    <hyperlink ref="H85" r:id="rId84"/>
-    <hyperlink ref="H86" r:id="rId85"/>
-    <hyperlink ref="H87" r:id="rId86"/>
-    <hyperlink ref="H88" r:id="rId87"/>
-    <hyperlink ref="H89" r:id="rId88"/>
-    <hyperlink ref="H90" r:id="rId89"/>
-    <hyperlink ref="H91" r:id="rId90"/>
-    <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5394,8 +4591,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5431,10 +4628,10 @@
         <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5442,18 +4639,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5461,18 +4658,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5480,18 +4677,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5499,18 +4696,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>257</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5518,18 +4715,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>185</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>273</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5537,18 +4734,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>190</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5556,144 +4753,11 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>361</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5702,13 +4766,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5722,23 +4779,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5746,7 +4803,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>388</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3">
         <v>14</v>
@@ -5754,7 +4811,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>333</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -5762,15 +4819,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>390</v>
+        <v>335</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5778,15 +4835,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>216</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>392</v>
+        <v>336</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5794,7 +4851,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5802,7 +4859,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5810,7 +4867,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>339</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -5826,7 +4883,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5834,7 +4891,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>396</v>
+        <v>341</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5842,7 +4899,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>397</v>
+        <v>342</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5864,7 +4921,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
@@ -5885,15 +4942,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -5901,7 +4958,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5909,7 +4966,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5917,7 +4974,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5925,7 +4982,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5933,7 +4990,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5941,7 +4998,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5949,7 +5006,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>211</v>
+        <v>297</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5957,34 +5014,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>214</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>220</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>245</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>304</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5995,23 +5052,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>344</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>345</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>398</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
@@ -6103,13 +5160,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6117,13 +5174,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C9" s="3">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -6131,10 +5188,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
       <c r="C10" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -6145,10 +5202,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -6159,10 +5216,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -6173,10 +5230,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -6187,10 +5244,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6201,10 +5258,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -6215,13 +5272,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>325</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.0</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6241,15 +5298,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>346</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6263,10 +5320,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -6274,10 +5331,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -6296,7 +5353,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
@@ -6304,7 +5361,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -6312,12 +5369,12 @@
         <v>115</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6325,23 +5382,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>289</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6349,15 +5406,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>258</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6384,10 +5441,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>344</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>350</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6399,10 +5456,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>406</v>
+        <v>351</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>352</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6419,31 +5476,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>304</v>
+        <v>246</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>409</v>
+        <v>355</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>308</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3">
@@ -6451,31 +5508,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>410</v>
+        <v>315</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>411</v>
+        <v>316</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>412</v>
+        <v>358</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>414</v>
+        <v>318</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>415</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
@@ -6483,31 +5540,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>416</v>
+        <v>361</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>419</v>
+        <v>364</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>241</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
@@ -6515,31 +5572,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>423</v>
+        <v>369</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>118</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
@@ -6547,31 +5604,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="F6" s="3">
         <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>424</v>
+        <v>371</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>426</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
@@ -6579,31 +5636,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="3">
+        <v>74</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F7" s="3">
-        <v>76</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>427</v>
+        <v>377</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>426</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
@@ -6611,31 +5668,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>428</v>
+        <v>378</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>429</v>
+        <v>379</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>434</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -6643,31 +5700,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>435</v>
+        <v>370</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>439</v>
+        <v>385</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -6675,31 +5732,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>442</v>
+        <v>388</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>443</v>
+        <v>389</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -6707,31 +5764,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>444</v>
+        <v>391</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="F11" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>445</v>
+        <v>392</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>446</v>
+        <v>393</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -6739,31 +5796,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>137</v>
+        <v>396</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>412</v>
+        <v>363</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>449</v>
+        <v>397</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>450</v>
+        <v>398</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>83</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13">
@@ -6771,31 +5828,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="F13" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>455</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14">
@@ -6803,31 +5860,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>456</v>
+        <v>373</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>457</v>
+        <v>405</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>137</v>
+        <v>406</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15">
@@ -6835,31 +5892,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>461</v>
+        <v>373</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>463</v>
+        <v>411</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>227</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -6867,31 +5924,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>464</v>
+        <v>373</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>465</v>
+        <v>412</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>466</v>
+        <v>410</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>468</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
@@ -6899,31 +5956,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>435</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>469</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>470</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="F17" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>471</v>
+        <v>414</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>472</v>
+        <v>61</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>473</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -6931,31 +5988,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>416</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>474</v>
+        <v>417</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>475</v>
+        <v>418</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -6963,31 +6020,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>476</v>
+        <v>420</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>474</v>
+        <v>421</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>477</v>
+        <v>422</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
     </row>
     <row r="20">
@@ -6995,31 +6052,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>424</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>425</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>61</v>
+        <v>427</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21">
@@ -7027,31 +6084,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>479</v>
+        <v>366</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>342</v>
+        <v>429</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>172</v>
+        <v>430</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>480</v>
+        <v>431</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
